--- a/config/yunying/luxurydirectbuygift.xlsx
+++ b/config/yunying/luxurydirectbuygift.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="luxurydirectbuygift" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="luxurydirectbuygift" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>初心者限定パック</t>
+          <t>初学者限定包</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1366,10 +1366,9 @@
           <t>Rookie Limited Pack</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>初心者パック</t>
+          <t>初学者包</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1382,7 +1381,6 @@
           <t>Rookie Pack</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>1</t>
@@ -1403,7 +1401,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>1000</t>
@@ -1438,7 +1435,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1451,10 +1448,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>10+パック</t>
+          <t>10+包</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1467,7 +1463,6 @@
           <t>10+ Pack</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>1</t>
@@ -1493,7 +1488,6 @@
           <t>102</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>100</t>
@@ -1523,7 +1517,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1536,10 +1530,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>20+パック</t>
+          <t>20+包</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1552,7 +1545,6 @@
           <t>20+ Pack</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>1</t>
@@ -1573,7 +1565,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>3000</t>
@@ -1608,7 +1599,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1621,10 +1612,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>30+パック</t>
+          <t>30+包</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1637,7 +1627,6 @@
           <t>30+ Pack</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1663,7 +1652,6 @@
           <t>104</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>100</t>
@@ -1693,7 +1681,7 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1706,10 +1694,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>40+パック</t>
+          <t>40+包</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1722,7 +1709,6 @@
           <t>40+ Pack</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>1</t>
@@ -1748,7 +1734,6 @@
           <t>105</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>100</t>
@@ -1778,7 +1763,7 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1791,10 +1776,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>50+パック</t>
+          <t>50+包</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1807,7 +1791,6 @@
           <t>50+ Pack</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>1</t>
@@ -1833,7 +1816,6 @@
           <t>106</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>100</t>
@@ -1863,7 +1845,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1876,10 +1858,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>60+パック</t>
+          <t>60+包</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1892,7 +1873,6 @@
           <t>60+ Pack</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>1</t>
@@ -1918,7 +1898,6 @@
           <t>107</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>100</t>
@@ -1948,7 +1927,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1961,10 +1940,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>70+パック</t>
+          <t>70+包</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1977,7 +1955,6 @@
           <t>70+ Pack</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>1</t>
@@ -2003,7 +1980,6 @@
           <t>108</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>100</t>
@@ -2033,7 +2009,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2046,10 +2022,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>80+パック</t>
+          <t>80+包</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2062,7 +2037,6 @@
           <t>80+ Pack</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>1</t>
@@ -2088,7 +2062,6 @@
           <t>109</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>100</t>
@@ -2118,7 +2091,7 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2131,10 +2104,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>90+パック</t>
+          <t>90+包</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2147,7 +2119,6 @@
           <t>90+ Pack</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>1</t>
@@ -2173,7 +2144,6 @@
           <t>110</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>100</t>
@@ -2203,7 +2173,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2216,10 +2186,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>100+パック</t>
+          <t>100+包</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2232,7 +2201,6 @@
           <t>100+ Pack</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>1</t>
@@ -2258,7 +2226,6 @@
           <t>111</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>100</t>
@@ -2288,7 +2255,7 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>MAXパック</t>
+          <t>MAX包</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2301,10 +2268,9 @@
           <t>MAX Pack</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>最大レベルパック</t>
+          <t>最大级别包</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2317,7 +2283,6 @@
           <t>Max Level Pack</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>1</t>
@@ -2343,7 +2308,6 @@
           <t>112</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>100</t>
@@ -2373,7 +2337,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2386,10 +2350,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>ブロンズvipの星</t>
+          <t>青铜vip之星</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2402,7 +2365,6 @@
           <t>Bronze VIP Star</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>2</t>
@@ -2423,7 +2385,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>2000</t>
@@ -2458,7 +2419,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2471,10 +2432,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>シルバーvipの星</t>
+          <t>银色vip之星</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2487,7 +2447,6 @@
           <t>Silver VIP Star</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>2</t>
@@ -2513,7 +2472,6 @@
           <t>108</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>100</t>
@@ -2543,7 +2501,7 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2556,10 +2514,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>ゴールドvipの星</t>
+          <t>黄金vip之星</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2572,7 +2529,6 @@
           <t>Gold VIP Star</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>2</t>
@@ -2593,7 +2549,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>4000</t>
@@ -2628,7 +2583,7 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2641,10 +2596,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>プラチナvipの星</t>
+          <t>白金vip之星</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2657,7 +2611,6 @@
           <t>Platinum VIP Star</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>2</t>
@@ -2683,7 +2636,6 @@
           <t>110</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>100</t>
@@ -2713,7 +2665,7 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2726,10 +2678,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>ダイヤvipの星</t>
+          <t>钻石vip之星</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2742,7 +2693,6 @@
           <t>Diamond VIP Star</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>2</t>
@@ -2768,7 +2718,6 @@
           <t>111</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>100</t>
@@ -2798,7 +2747,7 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2811,10 +2760,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>王者vipの星</t>
+          <t>王者vip之星</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2827,7 +2775,6 @@
           <t>King VIP Star</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>2</t>
@@ -2853,7 +2800,6 @@
           <t>112</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>100</t>
@@ -2883,7 +2829,7 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2896,10 +2842,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>Lv.1スパイ掌握者</t>
+          <t>Lv.1间谍掌控者</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2912,7 +2857,6 @@
           <t>Spy Master I</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>3</t>
@@ -2933,7 +2877,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
           <t>3000</t>
@@ -2968,7 +2911,7 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2981,10 +2924,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>Lv.2スパイ掌握者</t>
+          <t>Lv.2间谍掌控者</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2997,7 +2939,6 @@
           <t>Spy Master II</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>3</t>
@@ -3023,7 +2964,6 @@
           <t>107</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>100</t>
@@ -3053,7 +2993,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3066,10 +3006,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>Lv.3スパイ掌握者</t>
+          <t>Lv.3间谍掌控者</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3082,7 +3021,6 @@
           <t>Spy Master III</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>3</t>
@@ -3103,7 +3041,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>6000</t>
@@ -3138,7 +3075,7 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3151,10 +3088,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>Lv.4スパイ掌握者</t>
+          <t>Lv.4间谍掌控者</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3167,7 +3103,6 @@
           <t>Spy Master IV</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>3</t>
@@ -3193,7 +3128,6 @@
           <t>109</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>100</t>
@@ -3223,7 +3157,7 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3236,10 +3170,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>Lv.5スパイ掌握者</t>
+          <t>Lv.5间谍掌控者</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3252,7 +3185,6 @@
           <t>Spy Master V</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>3</t>
@@ -3278,7 +3210,6 @@
           <t>110</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>100</t>
@@ -3308,7 +3239,7 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3321,10 +3252,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>Lv.6スパイ掌握者</t>
+          <t>Lv.6间谍掌控者</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3337,7 +3267,6 @@
           <t>Spy Master VI</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>3</t>
@@ -3363,7 +3292,6 @@
           <t>111</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>100</t>
@@ -3376,80 +3304,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" s="1" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" s="1" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" s="1" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" s="1" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3469,7 +3333,7 @@
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>初心者限定パック</t>
+          <t>初学者限定包</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3482,10 +3346,9 @@
           <t>Rookie Limited Pack</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>初心者パック</t>
+          <t>初学者包</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3498,7 +3361,6 @@
           <t>Rookie Pack</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>1</t>
@@ -3519,7 +3381,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
           <t>1000</t>
@@ -3554,7 +3415,7 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3567,10 +3428,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>10+パック</t>
+          <t>10+包</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3583,7 +3443,6 @@
           <t>10+ Pack</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>1</t>
@@ -3609,7 +3468,6 @@
           <t>102</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>100</t>
@@ -3639,7 +3497,7 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3652,10 +3510,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>20+パック</t>
+          <t>20+包</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3668,7 +3525,6 @@
           <t>20+ Pack</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>1</t>
@@ -3689,7 +3545,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
           <t>3000</t>
@@ -3724,7 +3579,7 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3737,10 +3592,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>30+パック</t>
+          <t>30+包</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3753,7 +3607,6 @@
           <t>30+ Pack</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>1</t>
@@ -3779,7 +3632,6 @@
           <t>104</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>100</t>
@@ -3809,7 +3661,7 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3822,10 +3674,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>40+パック</t>
+          <t>40+包</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3838,7 +3689,6 @@
           <t>40+ Pack</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>1</t>
@@ -3864,7 +3714,6 @@
           <t>105</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>100</t>
@@ -3894,7 +3743,7 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3907,10 +3756,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>50+パック</t>
+          <t>50+包</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3923,7 +3771,6 @@
           <t>50+ Pack</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>1</t>
@@ -3949,7 +3796,6 @@
           <t>106</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>100</t>
@@ -3979,7 +3825,7 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3992,10 +3838,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>60+パック</t>
+          <t>60+包</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4008,7 +3853,6 @@
           <t>60+ Pack</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>1</t>
@@ -4034,7 +3878,6 @@
           <t>107</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>100</t>
@@ -4064,7 +3907,7 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4077,10 +3920,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>70+パック</t>
+          <t>70+包</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4093,7 +3935,6 @@
           <t>70+ Pack</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>1</t>
@@ -4119,7 +3960,6 @@
           <t>108</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>100</t>
@@ -4149,7 +3989,7 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4162,10 +4002,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>80+パック</t>
+          <t>80+包</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4178,7 +4017,6 @@
           <t>80+ Pack</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>1</t>
@@ -4204,7 +4042,6 @@
           <t>109</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>100</t>
@@ -4234,7 +4071,7 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4247,10 +4084,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>90+パック</t>
+          <t>90+包</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4263,7 +4099,6 @@
           <t>90+ Pack</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>1</t>
@@ -4289,7 +4124,6 @@
           <t>110</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>100</t>
@@ -4319,7 +4153,7 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>レベルパック</t>
+          <t>等级包</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4332,10 +4166,9 @@
           <t>Level Pack</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>100+パック</t>
+          <t>100+包</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4348,7 +4181,6 @@
           <t>100+ Pack</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>1</t>
@@ -4374,7 +4206,6 @@
           <t>111</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>100</t>
@@ -4404,7 +4235,7 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>MAXパック</t>
+          <t>MAX包</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4417,10 +4248,9 @@
           <t>MAX Pack</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>最大レベルパック</t>
+          <t>最大级别包</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4433,7 +4263,6 @@
           <t>Max Level Pack</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>1</t>
@@ -4459,7 +4288,6 @@
           <t>112</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>100</t>
@@ -4489,7 +4317,7 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4502,10 +4330,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>ブロンズvipの星</t>
+          <t>青铜vip之星</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4518,7 +4345,6 @@
           <t>Bronze VIP Star</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>2</t>
@@ -4539,7 +4365,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
           <t>2000</t>
@@ -4574,7 +4399,7 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4587,10 +4412,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>シルバーvipの星</t>
+          <t>银色vip之星</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4603,7 +4427,6 @@
           <t>Silver VIP Star</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>2</t>
@@ -4629,7 +4452,6 @@
           <t>108</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>100</t>
@@ -4659,7 +4481,7 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4672,10 +4494,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>ゴールドvipの星</t>
+          <t>黄金vip之星</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4688,7 +4509,6 @@
           <t>Gold VIP Star</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>2</t>
@@ -4709,7 +4529,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
           <t>4000</t>
@@ -4744,7 +4563,7 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4757,10 +4576,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>プラチナvipの星</t>
+          <t>白金vip之星</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4773,7 +4591,6 @@
           <t>Platinum VIP Star</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>2</t>
@@ -4799,7 +4616,6 @@
           <t>110</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>100</t>
@@ -4829,7 +4645,7 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4842,10 +4658,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>ダイヤvipの星</t>
+          <t>钻石vip之星</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4858,7 +4673,6 @@
           <t>Diamond VIP Star</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>2</t>
@@ -4884,7 +4698,6 @@
           <t>111</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>100</t>
@@ -4914,7 +4727,7 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>貴族パック</t>
+          <t>贵族包</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4927,10 +4740,9 @@
           <t>Noble Pack</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>王者vipの星</t>
+          <t>王者vip之星</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4943,7 +4755,6 @@
           <t>King VIP Star</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>2</t>
@@ -4969,7 +4780,6 @@
           <t>112</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>100</t>
@@ -4999,7 +4809,7 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5012,10 +4822,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>Lv.1スパイ掌握者</t>
+          <t>Lv.1间谍掌控者</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5028,7 +4837,6 @@
           <t>Spy Master I</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>3</t>
@@ -5049,7 +4857,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
           <t>3000</t>
@@ -5084,7 +4891,7 @@
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5097,10 +4904,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>Lv.2スパイ掌握者</t>
+          <t>Lv.2间谍掌控者</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5113,7 +4919,6 @@
           <t>Spy Master II</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>3</t>
@@ -5139,7 +4944,6 @@
           <t>107</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>100</t>
@@ -5169,7 +4973,7 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5182,10 +4986,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>Lv.3スパイ掌握者</t>
+          <t>Lv.3间谍掌控者</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5198,7 +5001,6 @@
           <t>Spy Master III</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>3</t>
@@ -5219,7 +5021,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
           <t>6000</t>
@@ -5254,7 +5055,7 @@
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5267,10 +5068,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>Lv.4スパイ掌握者</t>
+          <t>Lv.4间谍掌控者</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5283,7 +5083,6 @@
           <t>Spy Master IV</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>3</t>
@@ -5309,7 +5108,6 @@
           <t>109</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
           <t>100</t>
@@ -5339,7 +5137,7 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5352,10 +5150,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>Lv.5スパイ掌握者</t>
+          <t>Lv.5间谍掌控者</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5368,7 +5165,6 @@
           <t>Spy Master V</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>3</t>
@@ -5394,7 +5190,6 @@
           <t>110</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
           <t>100</t>
@@ -5424,7 +5219,7 @@
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>スパイパック</t>
+          <t>间谍包</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5437,10 +5232,9 @@
           <t>Spy Pack</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>Lv.6スパイ掌握者</t>
+          <t>Lv.6间谍掌控者</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5453,7 +5247,6 @@
           <t>Spy Master VI</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>3</t>
@@ -5479,7 +5272,6 @@
           <t>111</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
           <t>100</t>
